--- a/teach_import_template.xlsx
+++ b/teach_import_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\school_timeTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72370160-D522-4FC3-9C9B-B4D48FB6A54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74064261-8A08-4813-9EBE-D5B9A802A1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>SuNT</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{D4EAADAF-B05E-40FB-BC60-259F7EFBC23B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>SuNT:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
   <si>
     <t>Họ và Tên</t>
   </si>
@@ -34,9 +68,6 @@
     <t>Email</t>
   </si>
   <si>
-    <t>Năm Sinh</t>
-  </si>
-  <si>
     <t>Địa Chỉ</t>
   </si>
   <si>
@@ -98,13 +129,67 @@
   </si>
   <si>
     <t>Bắc Giang</t>
+  </si>
+  <si>
+    <t>Trạng Thái</t>
+  </si>
+  <si>
+    <t>Đang hoạt động</t>
+  </si>
+  <si>
+    <t>Nghỉ hưu</t>
+  </si>
+  <si>
+    <t>Nghỉ phép dài hạn</t>
+  </si>
+  <si>
+    <t>Có thể dạy buổi sáng</t>
+  </si>
+  <si>
+    <t>Có thể dạy buổi chiều</t>
+  </si>
+  <si>
+    <t>Ngày không dạy được</t>
+  </si>
+  <si>
+    <t>Có</t>
+  </si>
+  <si>
+    <t>Không</t>
+  </si>
+  <si>
+    <t>Số tiết dạy tối đa 1 tuần</t>
+  </si>
+  <si>
+    <t>Thứ 2</t>
+  </si>
+  <si>
+    <t>Thứ 2, Thứ 4</t>
+  </si>
+  <si>
+    <t>Ngày Sinh</t>
+  </si>
+  <si>
+    <t>20/3/1989</t>
+  </si>
+  <si>
+    <t>23/4/2000</t>
+  </si>
+  <si>
+    <t>13/3/1997</t>
+  </si>
+  <si>
+    <t>21/5/1997</t>
+  </si>
+  <si>
+    <t>24/6/1996</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +218,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -187,7 +285,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
@@ -495,8 +593,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
@@ -504,9 +602,14 @@
     <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.44140625" customWidth="1"/>
     <col min="5" max="5" width="11.109375" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" customWidth="1"/>
+    <col min="9" max="9" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -520,110 +623,191 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>1234567890</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2">
-        <v>1989</v>
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>1234567890</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3">
-        <v>2000</v>
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>1234567890</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4">
-        <v>1997</v>
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>1234567890</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5">
-        <v>1997</v>
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>1234567890</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>1996</v>
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -636,5 +820,6 @@
     <hyperlink ref="D6" r:id="rId5" xr:uid="{942E1770-4587-4996-B57E-4A84C84A82BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>
--- a/teach_import_template.xlsx
+++ b/teach_import_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\school_timeTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\school_timeTable_v1.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74064261-8A08-4813-9EBE-D5B9A802A1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85931DD5-2848-47B1-9F29-09E5795C74C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,42 +19,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>SuNT</author>
-  </authors>
-  <commentList>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{D4EAADAF-B05E-40FB-BC60-259F7EFBC23B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>SuNT:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>Họ và Tên</t>
   </si>
@@ -62,15 +28,6 @@
     <t>Môn Dạy</t>
   </si>
   <si>
-    <t>Số Điện Thoại</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Địa Chỉ</t>
-  </si>
-  <si>
     <t>Nguyễn Văn Thắng</t>
   </si>
   <si>
@@ -86,51 +43,6 @@
     <t>Dương Đình Khải</t>
   </si>
   <si>
-    <t>Toán 10</t>
-  </si>
-  <si>
-    <t>Văn 11</t>
-  </si>
-  <si>
-    <t>Lý 12</t>
-  </si>
-  <si>
-    <t>Sử 10</t>
-  </si>
-  <si>
-    <t>Địa 11</t>
-  </si>
-  <si>
-    <t>thang@gmail.com</t>
-  </si>
-  <si>
-    <t>my@gmail.com</t>
-  </si>
-  <si>
-    <t>khai1@gmail.com</t>
-  </si>
-  <si>
-    <t>tan@gmail.com</t>
-  </si>
-  <si>
-    <t>khai2@gmail.com</t>
-  </si>
-  <si>
-    <t>Hà Nội</t>
-  </si>
-  <si>
-    <t>Thái Bình</t>
-  </si>
-  <si>
-    <t>Nghệ An</t>
-  </si>
-  <si>
-    <t>Nam Định</t>
-  </si>
-  <si>
-    <t>Bắc Giang</t>
-  </si>
-  <si>
     <t>Trạng Thái</t>
   </si>
   <si>
@@ -167,29 +79,44 @@
     <t>Thứ 2, Thứ 4</t>
   </si>
   <si>
-    <t>Ngày Sinh</t>
-  </si>
-  <si>
-    <t>20/3/1989</t>
-  </si>
-  <si>
-    <t>23/4/2000</t>
-  </si>
-  <si>
-    <t>13/3/1997</t>
-  </si>
-  <si>
-    <t>21/5/1997</t>
-  </si>
-  <si>
-    <t>24/6/1996</t>
+    <t>Mã GV</t>
+  </si>
+  <si>
+    <t>thangnv</t>
+  </si>
+  <si>
+    <t>myht</t>
+  </si>
+  <si>
+    <t>khaicd</t>
+  </si>
+  <si>
+    <t>tanmv</t>
+  </si>
+  <si>
+    <t>khaidk</t>
+  </si>
+  <si>
+    <t>Toán 11</t>
+  </si>
+  <si>
+    <t>Thể dục 11</t>
+  </si>
+  <si>
+    <t>Toán 10, Toán 11</t>
+  </si>
+  <si>
+    <t>Lý 11</t>
+  </si>
+  <si>
+    <t>Văn 12, Lý 11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,27 +137,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -276,9 +182,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -288,10 +193,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -593,233 +497,167 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" customWidth="1"/>
-    <col min="7" max="7" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" customWidth="1"/>
-    <col min="9" max="9" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>31</v>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>1234567890</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="H2">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>1234567890</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3">
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
-        <v>1234567890</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
-        <v>1234567890</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5">
-        <v>20</v>
-      </c>
-      <c r="I5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>1234567890</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>42</v>
-      </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{1E43D582-F1DD-4B72-B889-173E041005BB}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{5B799D52-DFE1-4C3E-8865-4E28CEA50D81}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{7068B1DA-2F5C-40D6-97CF-1F2BBCFEF237}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{0366D214-88E1-4490-BAF7-328948AF7EA5}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{942E1770-4587-4996-B57E-4A84C84A82BA}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>